--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.24007458830801</v>
+        <v>5.726512120600052</v>
       </c>
       <c r="D2" t="n">
-        <v>35.83769906536222</v>
+        <v>5.823626098121362</v>
       </c>
       <c r="E2" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F2" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.08834393411886</v>
+        <v>3.264355889294314</v>
       </c>
       <c r="D3" t="n">
-        <v>19.52491173914467</v>
+        <v>3.172798157611008</v>
       </c>
       <c r="E3" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.09885123842842</v>
+        <v>7.978563326244619</v>
       </c>
       <c r="D4" t="n">
-        <v>49.68690524430242</v>
+        <v>8.074122102199144</v>
       </c>
       <c r="E4" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F4" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.539541263160211</v>
+        <v>0.5751754552635343</v>
       </c>
       <c r="D5" t="n">
-        <v>3.318826463422794</v>
+        <v>0.5393093003062041</v>
       </c>
       <c r="E5" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F5" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.7511297624929</v>
+        <v>2.234558586405097</v>
       </c>
       <c r="D6" t="n">
-        <v>14.2162889674174</v>
+        <v>2.310146957205327</v>
       </c>
       <c r="E6" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F6" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.38800287899704</v>
+        <v>2.500550467837019</v>
       </c>
       <c r="D7" t="n">
-        <v>14.76558950310202</v>
+        <v>2.399408294254078</v>
       </c>
       <c r="E7" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F7" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.3077086748428</v>
+        <v>3.462502659661955</v>
       </c>
       <c r="D8" t="n">
-        <v>21.68614816512732</v>
+        <v>3.52399907683319</v>
       </c>
       <c r="E8" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F8" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.75615636398639</v>
+        <v>4.997875409147788</v>
       </c>
       <c r="D9" t="n">
-        <v>30.27256165863744</v>
+        <v>4.919291269528584</v>
       </c>
       <c r="E9" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F9" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.20980311263186</v>
+        <v>3.121593005802678</v>
       </c>
       <c r="D10" t="n">
-        <v>16.45554270875138</v>
+        <v>2.674025690172099</v>
       </c>
       <c r="E10" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F10" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.42217140461287</v>
+        <v>6.568602853249591</v>
       </c>
       <c r="D11" t="n">
-        <v>39.89275276994693</v>
+        <v>6.482572325116377</v>
       </c>
       <c r="E11" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F11" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.55625921083238</v>
+        <v>6.427892121760262</v>
       </c>
       <c r="D12" t="n">
-        <v>39.17092882539312</v>
+        <v>6.365275934126382</v>
       </c>
       <c r="E12" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F12" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.2697639562898</v>
+        <v>5.731336642897093</v>
       </c>
       <c r="D13" t="n">
-        <v>35.08651454474889</v>
+        <v>5.701558613521694</v>
       </c>
       <c r="E13" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F13" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.15744984198115</v>
+        <v>6.200585599321936</v>
       </c>
       <c r="D14" t="n">
-        <v>37.79596022798791</v>
+        <v>6.141843537048035</v>
       </c>
       <c r="E14" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F14" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.22513759668275</v>
+        <v>4.911584859460946</v>
       </c>
       <c r="D15" t="n">
-        <v>30.13234970954263</v>
+        <v>4.896506827800677</v>
       </c>
       <c r="E15" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F15" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.33451388648031</v>
+        <v>3.141858506553051</v>
       </c>
       <c r="D16" t="n">
-        <v>18.94755263102853</v>
+        <v>3.078977302542136</v>
       </c>
       <c r="E16" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F16" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.33985522156073</v>
+        <v>6.067726473503619</v>
       </c>
       <c r="D17" t="n">
-        <v>34.81572311441924</v>
+        <v>5.657555006093127</v>
       </c>
       <c r="E17" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F17" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.47000791720183</v>
+        <v>3.001376286545297</v>
       </c>
       <c r="D18" t="n">
-        <v>11.88719090816763</v>
+        <v>1.931668522577241</v>
       </c>
       <c r="E18" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F18" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>40.25548788332969</v>
+        <v>6.541516781041074</v>
       </c>
       <c r="D19" t="n">
-        <v>40.2531155320837</v>
+        <v>6.541131273963601</v>
       </c>
       <c r="E19" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F19" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>25.49162617947138</v>
+        <v>4.1423892541641</v>
       </c>
       <c r="D20" t="n">
-        <v>22.82971139346768</v>
+        <v>3.709828101438498</v>
       </c>
       <c r="E20" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F20" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>24.25410792238736</v>
+        <v>3.941292537387945</v>
       </c>
       <c r="D21" t="n">
-        <v>23.82866276274117</v>
+        <v>3.87215769894544</v>
       </c>
       <c r="E21" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F21" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>12.69678351287927</v>
+        <v>2.063227320842882</v>
       </c>
       <c r="D22" t="n">
-        <v>12.59969864856697</v>
+        <v>2.047451030392133</v>
       </c>
       <c r="E22" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F22" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>21.40592967590931</v>
+        <v>3.478463572335263</v>
       </c>
       <c r="D23" t="n">
-        <v>21.09043345167694</v>
+        <v>3.427195435897503</v>
       </c>
       <c r="E23" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F23" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>16.75338478263806</v>
+        <v>2.722425027178685</v>
       </c>
       <c r="D24" t="n">
-        <v>17.04415290869855</v>
+        <v>2.769674847663514</v>
       </c>
       <c r="E24" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F24" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>13.3100085817017</v>
+        <v>2.162876394526526</v>
       </c>
       <c r="D25" t="n">
-        <v>13.20471091815716</v>
+        <v>2.145765524200538</v>
       </c>
       <c r="E25" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F25" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>36.49074126907757</v>
+        <v>5.929745456225106</v>
       </c>
       <c r="D26" t="n">
-        <v>36.40386690199716</v>
+        <v>5.915628371574539</v>
       </c>
       <c r="E26" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F26" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>11.84937559224786</v>
+        <v>1.925523533740278</v>
       </c>
       <c r="D27" t="n">
-        <v>11.79032358673786</v>
+        <v>1.915927582844902</v>
       </c>
       <c r="E27" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F27" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>10.56865924940483</v>
+        <v>1.717407128028285</v>
       </c>
       <c r="D28" t="n">
-        <v>10.511393363018</v>
+        <v>1.708101421490424</v>
       </c>
       <c r="E28" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F28" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>36.74210031265236</v>
+        <v>5.970591300806009</v>
       </c>
       <c r="D29" t="n">
-        <v>37.11867153751606</v>
+        <v>6.031784124846361</v>
       </c>
       <c r="E29" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F29" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>18.89446736990571</v>
+        <v>3.070350947609678</v>
       </c>
       <c r="D30" t="n">
-        <v>19.3183175797548</v>
+        <v>3.139226606710155</v>
       </c>
       <c r="E30" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F30" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>28.43263669472208</v>
+        <v>4.620303462892338</v>
       </c>
       <c r="D31" t="n">
-        <v>28.87262607413236</v>
+        <v>4.691801737046509</v>
       </c>
       <c r="E31" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F31" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>31.37154096848091</v>
+        <v>5.097875407378148</v>
       </c>
       <c r="D32" t="n">
-        <v>31.28640427509268</v>
+        <v>5.084040694702561</v>
       </c>
       <c r="E32" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F32" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>24.73184191723632</v>
+        <v>4.018924311550903</v>
       </c>
       <c r="D33" t="n">
-        <v>25.056785490919</v>
+        <v>4.071727642274337</v>
       </c>
       <c r="E33" t="n">
-        <v>10.87205427078928</v>
+        <v>1.766708819003258</v>
       </c>
       <c r="F33" t="n">
-        <v>11.09162479410584</v>
+        <v>1.8023890290422</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
